--- a/output/pdf_financials_xlsx/PRME.xlsx
+++ b/output/pdf_financials_xlsx/PRME.xlsx
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.381242</v>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.742554</v>
       </c>
     </row>
     <row r="93">
@@ -3329,7 +3329,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>3.381242</v>
       </c>

--- a/output/pdf_financials_xlsx/PRME.xlsx
+++ b/output/pdf_financials_xlsx/PRME.xlsx
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022555</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.20895</v>
       </c>
     </row>
     <row r="13">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.004791</v>
+        <v>-0.982236</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-83.851388</v>
+        <v>-83.642438</v>
       </c>
     </row>
     <row r="28">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.004791</v>
+        <v>-0.982236</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-83.851388</v>
+        <v>-83.642438</v>
       </c>
     </row>
     <row r="30">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.678137</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.868395</v>
       </c>
     </row>
     <row r="35">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.678137</v>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.868395</v>
       </c>
     </row>
     <row r="37">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.69128</v>
+        <v>0.013143</v>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.906033</v>
+        <v>0.037638</v>
       </c>
     </row>
     <row r="49">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">

--- a/output/pdf_financials_xlsx/PRME.xlsx
+++ b/output/pdf_financials_xlsx/PRME.xlsx
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.004372</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.000735</v>
       </c>
     </row>
     <row r="29">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.982236</v>
+        <v>-0.977864</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-83.642438</v>
+        <v>-83.64170300000001</v>
       </c>
     </row>
     <row r="30">
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.004372</v>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.000735</v>
       </c>
     </row>
     <row r="101">
@@ -3552,7 +3552,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.000636</v>
       </c>
@@ -3581,7 +3585,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.003736</v>
       </c>
@@ -4589,7 +4597,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -4620,7 +4632,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PRME.xlsx
+++ b/output/pdf_financials_xlsx/PRME.xlsx
@@ -785,7 +785,7 @@
         <v>-1.004791</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-83.851388</v>
+        <v>-48.447367</v>
       </c>
     </row>
     <row r="21">
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-35.404021</v>
       </c>
     </row>
     <row r="22">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.1049</v>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.7004089999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00075</v>
       </c>
     </row>
     <row r="112">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00075</v>
       </c>
     </row>
     <row r="135">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-13.176089</v>
+        <v>-13.176839</v>
       </c>
     </row>
   </sheetData>
@@ -4091,7 +4091,11 @@
           <t>Acquisition of equipment 9</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -4888,7 +4892,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -4917,7 +4925,11 @@
           <t>Loss from discontinued operations 6</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
